--- a/employee_surveys/046_software_update_employee_insights_report--employee_surveys.xlsx
+++ b/employee_surveys/046_software_update_employee_insights_report--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>update_experiences</t>
+          <t>update_experience</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -555,7 +555,11 @@
           <t>What issues did you encounter</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>List the issues you faced</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -597,7 +601,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>contact_details</t>
+          <t>contact_preferred_method</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -605,7 +609,11 @@
           <t>How can we contact you</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Choose your preferred contact method</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>yes</t>
@@ -620,7 +628,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -643,7 +651,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email_address</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -684,17 +692,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>contact_meeting</t>
+          <t>meeting_time</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Meeting</t>
+          <t>Meeting Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -707,17 +715,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>contact_in_person</t>
+          <t>meeting_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>In person</t>
+          <t>Meeting Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -730,17 +738,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_chat</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Phone (2)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -758,12 +766,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>meeting</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -781,12 +789,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>In person</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,17 +807,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>contact_meeting_time</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Meeting Time</t>
+          <t>Chat</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -822,17 +830,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>contact_meeting_date</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Meeting Date</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -845,251 +853,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>meeting_time_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Meeting Time 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>contact_meeting</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Meeting</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>contact_in_person</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>In Person</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>contact_chat</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Chat</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>email_address</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>phone_number</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>contact_meeting_date</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Meeting Date</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>meeting_time</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Meeting Time</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>contact_meeting_time</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Meeting Time</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,10 +884,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1202,7 +980,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>contact_preferred_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1219,7 +997,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>contact_preferred_method_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1236,7 +1014,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>contact_preferred_method_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1253,7 +1031,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>contact_preferred_method_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1270,287 +1048,100 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>contact_details_choices</t>
+          <t>meeting_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>in_person</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>In Person</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>contact_meeting_choices</t>
+          <t>meeting_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>contact_meeting_choices</t>
+          <t>in_person_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>contact_in_person_choices</t>
+          <t>in_person_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>contact_in_person_choices</t>
+          <t>chat_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>contact_chat_choices</t>
+          <t>chat_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>contact_chat_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>contact_email_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>contact_email_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>contact_phone_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>contact_phone_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>contact_meeting_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>contact_meeting_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>contact_in_person_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>contact_in_person_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>contact_chat_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>contact_chat_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>False</t>
         </is>
